--- a/01-stakeholders/delivery/source/00-stakeholders.xlsx
+++ b/01-stakeholders/delivery/source/00-stakeholders.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\School21\BSA\BSA01_Stakeholders_ID_1361441-1\src\DELI_DeliveryService\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\School21\BSA01_Stakeholders_ID_1361441-1\src\DELI_DeliveryService\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605CDC7C-84FB-4985-B7D6-8D0F6C980276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A090A2-90E5-4704-A10F-E55D2E5496A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="1020" windowWidth="25185" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Каталог стейкхолдеров" sheetId="1" r:id="rId1"/>
-    <sheet name="Характеристики каталога" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог стейкхолдеров'!$A$1:$G$13</definedName>
@@ -29,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
-  <si>
-    <t>Идентификатор</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
   <si>
     <t>Заинтересованная сторона (ФИО, если известно)</t>
   </si>
@@ -113,36 +109,6 @@
   </si>
   <si>
     <t>Роскомнадзор</t>
-  </si>
-  <si>
-    <t>Характеристика</t>
-  </si>
-  <si>
-    <t>Назначение (почему выбрана)</t>
-  </si>
-  <si>
-    <t>Уникальный неизменяемый код стейкхолдера по шаблону STKYYYYY (STK — каталог стейкхолдеров; правила кодирования — по аналогии с каталогами INF и GLS проекта BSA 00). Позволяет ссылаться на стейкхолдера из других артефактов.</t>
-  </si>
-  <si>
-    <t>Наименование лица, группы или организации; ФИО конкретных людей в учебной задаче неизвестны.</t>
-  </si>
-  <si>
-    <t>Тип стейкхолдера — влияет на способ взаимодействия с ним.</t>
-  </si>
-  <si>
-    <t>Класс из таблицы 1 методички (выгодоприобретатели, пользователи, взаимодействующие стороны, регуляторы, команды сопровождения и разработки) — нужна для выявления ролей и контроля полноты: по каждому классу задается свой вопрос.</t>
-  </si>
-  <si>
-    <t>Уровень контактности с системой</t>
-  </si>
-  <si>
-    <t>Слой луковичной диаграммы (конечный пользователь / не общаются с системой / затрагиваемые внешние стороны / создают систему) — основа для Ex01.</t>
-  </si>
-  <si>
-    <t>Проектная роль по основной выполняемой функции (раздел 3.3); «нет» — если сторона в системе не работает.</t>
-  </si>
-  <si>
-    <t>Номер проекта, в котором стейкхолдер добавлен в каталог (по рекомендации задания — BSA 01).</t>
   </si>
   <si>
     <t>STA00001</t>
@@ -218,23 +184,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="8"/>
@@ -256,40 +212,20 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F5B7C"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -311,20 +247,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -630,395 +562,317 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="34" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17" style="6" customWidth="1"/>
-    <col min="5" max="6" width="28" style="6" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="34" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17" style="4" customWidth="1"/>
+    <col min="5" max="6" width="28" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="E2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>